--- a/artfynd/A 53852-2024 artfynd.xlsx
+++ b/artfynd/A 53852-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>118121146</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118121148</v>
+        <v>118103207</v>
       </c>
       <c r="B3" t="n">
-        <v>104925</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>608001</v>
+        <v>608076</v>
       </c>
       <c r="R3" t="n">
-        <v>7045655</v>
+        <v>7045645</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118121140</v>
+        <v>118103206</v>
       </c>
       <c r="B4" t="n">
-        <v>97750</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220093</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +904,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>608001</v>
+        <v>608076</v>
       </c>
       <c r="R4" t="n">
-        <v>7045655</v>
+        <v>7045645</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-06-30</t>
+          <t>2024-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,6 +963,200 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118121140</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rävelflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>608001</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7045655</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118121148</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rävelflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>608001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7045655</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
